--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
@@ -77544,13 +77544,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BFFC3E-1A4D-4E2C-B35D-3C2F7B310F4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA1DACDF-4A0B-4BBD-95BB-0EAD5447E415}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A83094-E3D8-4A59-9FD2-1A6E8339A1C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD3845F-04F8-4140-8534-B1FA00326320}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CCA8D03-F06E-445D-BFD9-23F8619ECBDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9244E291-DDAF-4B64-A5BB-0EF28E9684B6}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
@@ -77544,13 +77544,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA1DACDF-4A0B-4BBD-95BB-0EAD5447E415}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DD2DDD9-E616-41BF-8008-DC5EFEB39564}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD3845F-04F8-4140-8534-B1FA00326320}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95B9BA65-28B1-4F1E-950E-4D8EA84CDC8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9244E291-DDAF-4B64-A5BB-0EF28E9684B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56C758C-61CA-49A2-9317-E9DF0E2F047C}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
@@ -77544,13 +77544,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DD2DDD9-E616-41BF-8008-DC5EFEB39564}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BFFC3E-1A4D-4E2C-B35D-3C2F7B310F4D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95B9BA65-28B1-4F1E-950E-4D8EA84CDC8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A83094-E3D8-4A59-9FD2-1A6E8339A1C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56C758C-61CA-49A2-9317-E9DF0E2F047C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CCA8D03-F06E-445D-BFD9-23F8619ECBDF}"/>
 </file>